--- a/backtest_runs/20260410_193731/filter/AVN/AVN.xlsx
+++ b/backtest_runs/20260410_193731/filter/AVN/AVN.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-311.2999999999934</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>99688.70000000001</v>
@@ -633,7 +633,7 @@
         <v>-2023.449999999995</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>105323.23</v>
@@ -679,7 +679,7 @@
         <v>-7969.279999999996</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>97353.95000000001</v>
@@ -863,7 +863,7 @@
         <v>-3673.339999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>109774.82</v>
@@ -955,7 +955,7 @@
         <v>-1400.849999999987</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>109307.87</v>
@@ -1001,7 +1001,7 @@
         <v>-996.1600000000009</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>108311.71</v>
@@ -1047,7 +1047,7 @@
         <v>-280.1700000000106</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>108031.54</v>
@@ -1093,7 +1093,7 @@
         <v>-3642.209999999994</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>104389.33</v>
@@ -1185,7 +1185,7 @@
         <v>-6568.430000000009</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>102957.35</v>
@@ -1231,7 +1231,7 @@
         <v>-1836.67</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>101120.68</v>
@@ -1277,7 +1277,7 @@
         <v>-2677.179999999998</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>98443.5</v>
@@ -1415,7 +1415,7 @@
         <v>-2147.970000000004</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>101930.06</v>
@@ -1507,7 +1507,7 @@
         <v>-684.8599999999965</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>101307.46</v>
@@ -1645,7 +1645,7 @@
         <v>-4295.939999999997</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>106039.22</v>
